--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/econ0763/Downloads/JPE/JPE-Mitman-20221230/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6356C29B-8068-A742-989F-A7BFE25B9C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="146">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -36,6 +31,81 @@
     <t>Reproduced?</t>
   </si>
   <si>
+    <t>_data/_aux/bvar_data.R</t>
+  </si>
+  <si>
+    <t>_data/_aux/data_bvar.csv</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>_data/_aux/bvar_est.m</t>
+  </si>
+  <si>
+    <t>_data/_aux/prob_up_bvar.csv</t>
+  </si>
+  <si>
+    <t>_data/_aux/spf_data.m</t>
+  </si>
+  <si>
+    <t>_data/_aux/spf_prob_u.csv</t>
+  </si>
+  <si>
+    <t>Provided file; no code identified</t>
+  </si>
+  <si>
+    <t>_data/_aux/spf_infl_moments.csv</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>_data/_data/_data_var/CPIAUCSL_tmp.xls</t>
+  </si>
+  <si>
+    <t>_data/table_a10.R</t>
+  </si>
+  <si>
+    <t>_model/_aux/_models_tmp/calibration.csv</t>
+  </si>
+  <si>
+    <t>_data/_aux/sce_data.R</t>
+  </si>
+  <si>
+    <t>_data/_aux/data_sce.rda</t>
+  </si>
+  <si>
+    <t>_data/figure_1_ab_table_a7a9.R</t>
+  </si>
+  <si>
+    <t>_data/data_sce.mat</t>
+  </si>
+  <si>
+    <t>_data/figure_6_data.R</t>
+  </si>
+  <si>
+    <t>_model/_aux/_models_tmp/figure_6.csv</t>
+  </si>
+  <si>
+    <t>_model/make_shocks.m</t>
+  </si>
+  <si>
+    <t>_model/_aux/_models_tmp/NewShocks.mat; NE3Shocks3.mat</t>
+  </si>
+  <si>
+    <t>_model/_aux/_baseline/BKKS_start_runs.m; _model/_aux/_kvar/BKKS_start_runs.m</t>
+  </si>
+  <si>
+    <t>_model/_aux/_models_tmp/model_*.mat</t>
+  </si>
+  <si>
+    <t>_model/_aux/_baseline/InfoDecomposition.m</t>
+  </si>
+  <si>
+    <t>_model/_aux/_models_tmp/model_7009_decomp.mat</t>
+  </si>
+  <si>
     <t>Figure/Table #</t>
   </si>
   <si>
@@ -45,7 +115,349 @@
     <t>Line Number</t>
   </si>
   <si>
+    <t>Figure 1 (a), (b)</t>
+  </si>
+  <si>
+    <t>74; 112</t>
+  </si>
+  <si>
+    <t>Figure 1 (c), (d)</t>
+  </si>
+  <si>
+    <t>_data/figure_1_cd.R</t>
+  </si>
+  <si>
+    <t>70; 95</t>
+  </si>
+  <si>
+    <t>Figure 2 (a)</t>
+  </si>
+  <si>
+    <t>_data/figure_2_a.R</t>
+  </si>
+  <si>
+    <t>75; 109</t>
+  </si>
+  <si>
+    <t>Figure 2 (b)</t>
+  </si>
+  <si>
+    <t>_data/figure_2_b.R</t>
+  </si>
+  <si>
+    <t>94; 128</t>
+  </si>
+  <si>
+    <t>Table I</t>
+  </si>
+  <si>
+    <t>_model/table_i_and_ii.m</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>Figure 3</t>
+  </si>
+  <si>
+    <t>_model/figure_3_and_4.m</t>
+  </si>
+  <si>
+    <t>172; 248</t>
+  </si>
+  <si>
+    <t>Figure 4</t>
+  </si>
+  <si>
+    <t>318; 388</t>
+  </si>
+  <si>
+    <t>Figure 5</t>
+  </si>
+  <si>
+    <t>_model/figure_5.m</t>
+  </si>
+  <si>
+    <t>121; 184</t>
+  </si>
+  <si>
+    <t>Figure 6</t>
+  </si>
+  <si>
+    <t>_data/figure_6_data.R; _model/figure_6.m</t>
+  </si>
+  <si>
+    <t>62; 131</t>
+  </si>
+  <si>
+    <t>Table II</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Figure 7</t>
+  </si>
+  <si>
+    <t>_model/figure_7.m</t>
+  </si>
+  <si>
+    <t>250; 265; 283; 301</t>
+  </si>
+  <si>
+    <t>Table III</t>
+  </si>
+  <si>
+    <t>_data/make_table3_data.do; _model/table_iii.m</t>
+  </si>
+  <si>
+    <t>197; 13-14; 72</t>
+  </si>
+  <si>
+    <t>Figure 8</t>
+  </si>
+  <si>
+    <t>_model/figure_8.m</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>Table IV</t>
+  </si>
+  <si>
+    <t>_model/table_iv.m</t>
+  </si>
+  <si>
+    <t>Table V</t>
+  </si>
+  <si>
+    <t>No new output; summary of Online Appendix C</t>
+  </si>
+  <si>
+    <t>Table VI</t>
+  </si>
+  <si>
+    <t>_model/table_vi.m</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Table A.7</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>Table A.8</t>
+  </si>
+  <si>
+    <t>_data/table_a8.R</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Table A.9</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Table A.10</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Table B.1</t>
+  </si>
+  <si>
+    <t>_model/_aux/_baseline/modelsMasterExcel.xlsx; _model/_aux/_kvar/modelsMasterExcel.xlsx</t>
+  </si>
+  <si>
+    <t>Table B.2</t>
+  </si>
+  <si>
+    <t>_data/table_b2_a.m; _model/table_bii.m</t>
+  </si>
+  <si>
+    <t>56; 104</t>
+  </si>
+  <si>
+    <t>Figure B.1</t>
+  </si>
+  <si>
+    <t>_model/figure_b1.m</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Figure B.2</t>
+  </si>
+  <si>
+    <t>_model/figure_b2.m</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>Table C.1</t>
+  </si>
+  <si>
+    <t>_model/table_ci.m</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Table C.2</t>
+  </si>
+  <si>
+    <t>_model/table_cii.m</t>
+  </si>
+  <si>
+    <t>Figure C.1</t>
+  </si>
+  <si>
+    <t>_model/figure_c1.m</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>Table C.3</t>
+  </si>
+  <si>
+    <t>_model/table_ciii.m</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Table C.4</t>
+  </si>
+  <si>
+    <t>_model/table_civ.m</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Table C.5</t>
+  </si>
+  <si>
+    <t>_model/table_cv.m</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Table C.6</t>
+  </si>
+  <si>
+    <t>_model/table_cvi.m</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Table C.7</t>
+  </si>
+  <si>
+    <t>_model/table_cvii.m</t>
+  </si>
+  <si>
+    <t>Figure C.2</t>
+  </si>
+  <si>
+    <t>_model/figure_c2.m</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Table C.8</t>
+  </si>
+  <si>
+    <t>_model/table_cviii.m</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Figure C.3</t>
+  </si>
+  <si>
+    <t>_model/figure_c3.m</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Table C.9</t>
+  </si>
+  <si>
+    <t>_model/table_cix.m</t>
+  </si>
+  <si>
+    <t>Figure C.4</t>
+  </si>
+  <si>
+    <t>_model/figure_c4.m</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Table C.10</t>
+  </si>
+  <si>
+    <t>_model/table_cx.m</t>
+  </si>
+  <si>
+    <t>Table C.11</t>
+  </si>
+  <si>
+    <t>_model/_aux/_baseline/InfoDecomposition.m; _model/table_cxi.m</t>
+  </si>
+  <si>
+    <t>59; 80</t>
+  </si>
+  <si>
+    <t>Table C.12</t>
+  </si>
+  <si>
+    <t>_model/table_cxii.m</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Figure D.1</t>
+  </si>
+  <si>
+    <t>_model/figure_d1.m</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Table D.1</t>
+  </si>
+  <si>
+    <t>_model/table_di.m</t>
+  </si>
+  <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t>Partially</t>
+  </si>
+  <si>
+    <t>p. 37: 2022 SCF wealth Gini is around 0.80</t>
   </si>
 </sst>
 </file>
@@ -55,26 +467,30 @@
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -89,23 +505,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -128,44 +541,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -192,32 +605,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -244,24 +639,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -273,239 +650,993 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="72" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
+    <row r="17" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="62" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>